--- a/samples/xlsx/中文示例_xlsx_01.xlsx
+++ b/samples/xlsx/中文示例_xlsx_01.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">

--- a/samples/xlsx/中文示例_xlsx_01.xlsx
+++ b/samples/xlsx/中文示例_xlsx_01.xlsx
@@ -492,91 +492,91 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>王桂芝</t>
+          <t>朱X</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>示例市001</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>na52@example.com</t>
+          <t>user001@example.com</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>13220111173</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>房地产项目招投标</t>
+          <t>硬件工程师</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>同兴万点信息有限公司</t>
+          <t>示例公司001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>赵萍</t>
+          <t>张X</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>太原县</t>
+          <t>示例市002</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>dufang@example.net</t>
+          <t>user002@example.com</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>15679358891</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>电脑维修</t>
+          <t>刨工</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>凌云科技有限公司</t>
+          <t>示例公司002</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>刘红</t>
+          <t>唐X</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -586,123 +586,123 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>示例市003</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>bren@example.net</t>
+          <t>user003@example.com</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13608411877</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>技工</t>
+          <t>培训督导</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>万迅电脑科技有限公司</t>
+          <t>示例公司003</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>张春梅</t>
+          <t>周X</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>磊县</t>
+          <t>示例市004</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>xiuyingfeng@example.net</t>
+          <t>user004@example.com</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18196895518</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>发动机/总装工程师</t>
+          <t>动力总成工程师</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>方正科技科技有限公司</t>
+          <t>示例公司004</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>张桂香</t>
+          <t>吴XX</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>示例市005</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>gujun@example.org</t>
+          <t>user005@example.com</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18840687271</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>需求工程师</t>
+          <t>金融/经济研究员</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>群英网络有限公司</t>
+          <t>示例公司005</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>常婷婷</t>
+          <t>王XX</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -712,81 +712,81 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>张家港县</t>
+          <t>示例市006</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>xieming@example.org</t>
+          <t>user006@example.com</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15620323737</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>项目经理/主管</t>
+          <t>折弯工</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>佳禾网络有限公司</t>
+          <t>示例公司006</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>周红霞</t>
+          <t>朱X</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>昆明县</t>
+          <t>示例市007</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>tianchao@example.com</t>
+          <t>user007@example.com</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18020501721</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>研究生</t>
+          <t>建筑制图/模型/渲染</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>鑫博腾飞科技有限公司</t>
+          <t>示例公司007</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>郝丽丽</t>
+          <t>张XX</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -796,81 +796,81 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>成县</t>
+          <t>示例市008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>gangzhao@example.com</t>
+          <t>user008@example.com</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15684226814</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>预结算员</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>联软传媒有限公司</t>
+          <t>示例公司008</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>邓超</t>
+          <t>于XX</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>畅县</t>
+          <t>示例市009</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>pengming@example.org</t>
+          <t>user009@example.com</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15909600763</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>人事主管</t>
+          <t>销售人员</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>天益科技有限公司</t>
+          <t>示例公司009</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>程飞</t>
+          <t>马XX</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -880,86 +880,86 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>示例市010</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>moyong@example.org</t>
+          <t>user010@example.com</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18025392039</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>汽车喷漆</t>
+          <t>保险业务经理/主管</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>快讯科技有限公司</t>
+          <t>示例公司010</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>陈岩</t>
+          <t>孙XX</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>荆门县</t>
+          <t>示例市011</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>taoguo@example.org</t>
+          <t>user011@example.com</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18214828924</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>项目总监</t>
+          <t>客户代表</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>商软冠联信息有限公司</t>
+          <t>示例公司011</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>曹畅</t>
+          <t>朱X</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -969,76 +969,76 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>合肥县</t>
+          <t>示例市012</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>juan40@example.org</t>
+          <t>user012@example.com</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18568034897</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>选址拓展/新店开发</t>
+          <t>印刷工</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>明腾网络有限公司</t>
+          <t>示例公司012</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>张杨</t>
+          <t>宋XX</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>峰市</t>
+          <t>示例市013</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>yuanjie@example.net</t>
+          <t>user013@example.com</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15261548137</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>列车/地铁司机</t>
+          <t>行政主厨/厨师长</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>泰麒麟传媒有限公司</t>
+          <t>示例公司013</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>赵X</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1048,39 +1048,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>贵阳县</t>
+          <t>示例市014</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ping58@example.net</t>
+          <t>user014@example.com</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15801021128</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>结构/土木/土建工程师</t>
+          <t>医疗器械市场推广</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>商软冠联传媒有限公司</t>
+          <t>示例公司014</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>谭冬梅</t>
+          <t>李XX</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1090,207 +1090,207 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>兰英县</t>
+          <t>示例市015</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>xia51@example.com</t>
+          <t>user015@example.com</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13057005081</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>锅炉工程师/技师</t>
+          <t>保险理赔</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>快讯信息有限公司</t>
+          <t>示例公司015</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>袁斌</t>
+          <t>张XX</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>瑜市</t>
+          <t>示例市016</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>panjuan@example.net</t>
+          <t>user016@example.com</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15567946114</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>系统集成工程师</t>
+          <t>学徒工</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>天开传媒有限公司</t>
+          <t>示例公司016</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>王玲</t>
+          <t>徐X</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>红县</t>
+          <t>示例市017</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>yong08@example.org</t>
+          <t>user017@example.com</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15616757374</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>快递员</t>
+          <t>饲养员</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>济南亿次元传媒有限公司</t>
+          <t>示例公司017</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>陈萍</t>
+          <t>孙X</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>磊市</t>
+          <t>示例市018</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>pqian@example.com</t>
+          <t>user018@example.com</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18986423561</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>数码直印/菲林输出</t>
+          <t>酒店/宾馆经理</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>精芯网络有限公司</t>
+          <t>示例公司018</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>张坤</t>
+          <t>唐XX</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>俊市</t>
+          <t>示例市019</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>wshen@example.org</t>
+          <t>user019@example.com</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18207896382</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>美容保健</t>
+          <t>喷塑工</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>四通网络有限公司</t>
+          <t>示例公司019</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>姬建平</t>
+          <t>李X</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1300,81 +1300,81 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>秀华县</t>
+          <t>示例市020</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>renguiying@example.org</t>
+          <t>user020@example.com</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18043859160</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>工程造价师/预结算经理</t>
+          <t>模具工</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>MBP软件科技有限公司</t>
+          <t>示例公司020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>奚琳</t>
+          <t>梁XX</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>桂芳市</t>
+          <t>示例市021</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>jiefan@example.org</t>
+          <t>user021@example.com</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15156981829</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>市场/营销/拓展总监</t>
+          <t>旅游产品销售</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>艾提科信信息有限公司</t>
+          <t>示例公司021</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>杨玉梅</t>
+          <t>萧XX</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1384,81 +1384,81 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>北镇县</t>
+          <t>示例市022</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>jun82@example.com</t>
+          <t>user022@example.com</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13592059716</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>安全员</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>诺依曼软件网络有限公司</t>
+          <t>示例公司022</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>傅彬</t>
+          <t>唐X</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>佛山市</t>
+          <t>示例市023</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>qiang92@example.org</t>
+          <t>user023@example.com</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18508646543</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>运输经理/主管</t>
+          <t>行政总监</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>联软科技有限公司</t>
+          <t>示例公司023</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>李桂香</t>
+          <t>马X</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1468,39 +1468,39 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>建平市</t>
+          <t>示例市024</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>guiyingguo@example.org</t>
+          <t>user024@example.com</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18526524529</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>专科医生</t>
+          <t>演员/群众演员</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>巨奥科技有限公司</t>
+          <t>示例公司024</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>吴玉梅</t>
+          <t>冯XX</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1510,123 +1510,123 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>示例市025</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>xiuying08@example.org</t>
+          <t>user025@example.com</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13443465271</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>电子技术研发工程师</t>
+          <t>大学教授</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>精芯网络有限公司</t>
+          <t>示例公司025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>曹雪</t>
+          <t>徐XX</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>佳市</t>
+          <t>示例市026</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>pyang@example.com</t>
+          <t>user026@example.com</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13798609570</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>艺术指导/舞台美术设计</t>
+          <t>锅炉工</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>七喜网络有限公司</t>
+          <t>示例公司026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>李敏</t>
+          <t>赵X</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>帅市</t>
+          <t>示例市027</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>xiaye@example.com</t>
+          <t>user027@example.com</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13861908367</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>培训</t>
+          <t>测试员</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>方正科技网络有限公司</t>
+          <t>示例公司027</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>余桂荣</t>
+          <t>吴XX</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1636,39 +1636,39 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>博市</t>
+          <t>示例市028</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>fangfeng@example.com</t>
+          <t>user028@example.com</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18058317115</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>收银主管</t>
+          <t>化妆品研发</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>易动力信息有限公司</t>
+          <t>示例公司028</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>彭丽娟</t>
+          <t>高XX</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1678,74 +1678,74 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>建县</t>
+          <t>示例市029</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>wei67@example.org</t>
+          <t>user029@example.com</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18833084085</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>茶艺师</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>新格林耐特传媒有限公司</t>
+          <t>示例公司029</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>周岩</t>
+          <t>萧XX</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>兴安盟市</t>
+          <t>示例市030</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>xiuying96@example.net</t>
+          <t>user030@example.com</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13199674621</t>
+          <t>0000-00000000</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>瘦身顾问</t>
+          <t>网店/淘宝客服</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>国讯网络有限公司</t>
+          <t>示例公司030</t>
         </is>
       </c>
     </row>

--- a/samples/xlsx/中文示例_xlsx_01.xlsx
+++ b/samples/xlsx/中文示例_xlsx_01.xlsx
@@ -492,17 +492,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>朱X</t>
+          <t>马X</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>张X</t>
+          <t>萧X</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -576,17 +576,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>唐X</t>
+          <t>于XX</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -618,17 +618,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>周X</t>
+          <t>孙XX</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>吴XX</t>
+          <t>刘X</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -702,17 +702,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>王XX</t>
+          <t>吴X</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -744,17 +744,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>朱X</t>
+          <t>李XX</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -786,17 +786,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>张XX</t>
+          <t>赵X</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>于XX</t>
+          <t>胡XX</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>马XX</t>
+          <t>孙X</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>孙XX</t>
+          <t>林XX</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>朱X</t>
+          <t>郭X</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -996,17 +996,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>宋XX</t>
+          <t>徐XX</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>赵X</t>
+          <t>于X</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1080,17 +1080,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>李XX</t>
+          <t>林XX</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>张XX</t>
+          <t>林XX</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>徐X</t>
+          <t>谢X</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>孙X</t>
+          <t>唐X</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>唐XX</t>
+          <t>李X</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>李X</t>
+          <t>胡X</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>梁XX</t>
+          <t>朱X</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>萧XX</t>
+          <t>朱X</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>唐X</t>
+          <t>陈X</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>马X</t>
+          <t>郑X</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1500,17 +1500,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>冯XX</t>
+          <t>宋XX</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>徐XX</t>
+          <t>吴XX</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>赵X</t>
+          <t>郭X</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1626,17 +1626,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>吴XX</t>
+          <t>黄X</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1668,17 +1668,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>高XX</t>
+          <t>张X</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1710,17 +1710,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>萧XX</t>
+          <t>孙X</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">

--- a/samples/xlsx/中文示例_xlsx_01.xlsx
+++ b/samples/xlsx/中文示例_xlsx_01.xlsx
@@ -492,17 +492,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>马X</t>
+          <t>董XX</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -534,17 +534,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>萧X</t>
+          <t>宋X</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>于XX</t>
+          <t>孙X</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -618,17 +618,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>孙XX</t>
+          <t>韩X</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>刘X</t>
+          <t>于XX</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>吴X</t>
+          <t>冯XX</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -744,17 +744,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>李XX</t>
+          <t>王X</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -786,17 +786,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>赵X</t>
+          <t>董XX</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>胡XX</t>
+          <t>冯X</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>孙X</t>
+          <t>吴XX</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>林XX</t>
+          <t>宋XX</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>郭X</t>
+          <t>刘XX</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -996,17 +996,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>徐XX</t>
+          <t>张X</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>于X</t>
+          <t>刘X</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1080,17 +1080,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>林XX</t>
+          <t>宋XX</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1122,17 +1122,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>林XX</t>
+          <t>张X</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1164,17 +1164,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>谢X</t>
+          <t>李XX</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>唐X</t>
+          <t>张XX</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1290,17 +1290,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>胡X</t>
+          <t>宋XX</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>朱X</t>
+          <t>张XX</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1416,17 +1416,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>陈X</t>
+          <t>黄XX</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>郑X</t>
+          <t>徐XX</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>吴XX</t>
+          <t>赵XX</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1584,17 +1584,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>郭X</t>
+          <t>胡XX</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1626,17 +1626,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>黄X</t>
+          <t>徐X</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>张X</t>
+          <t>高X</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1710,17 +1710,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>孙X</t>
+          <t>李XX</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
